--- a/results/gap_matrix.xlsx
+++ b/results/gap_matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gap_matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="evidence" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gap_matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,940 +561,517 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hasan, H. A., Al-Hussayni, K. H., &amp; Matloob, A. Z. K. (2025). Attention Mapping for Hallucination Reduction in Arabic Financial Using Retrieval-Augmented Generation Systems. Journal of Intelligent Informatics, Networking, and Cybersecurity 1(2). https://doi.org/10.65445/3106-1192.1006</t>
+          <t>Zhao, Y., Singh, P., Bhathena, H., et al. (2024). Optimizing LLM Based Retrieval Augmented Generation Pipelines in the Financial Domain. NAACL 2024 Industry Track, 279-294. https://doi.org/10.18653/v1/2024.naacl-industry.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Penelitian ini mengatasi masalah halusinasi pada sistem Retrieval-Augmented Generation (RAG) bahasa Arab untuk analisis dokumen keuangan.</t>
+          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Domain keuangan, dokumen finansial berbahasa Arab, dengan dataset baru berisi 7.000 pasangan query-konteks beranotasi.</t>
+          <t>Studi menggunakan dua dataset RAG dari sektor perbankan: halaman web publik tentang produk perbankan dan panduan kebijakan internal, keduanya berbahasa Inggris.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metode memperluas MarBERT dengan mekanisme supervisi perhatian dua tahap dan loss yang sadar halusinasi, serta ambang presisi dinamis untuk penolakan output.</t>
+          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan akurasi klasifikasi 95.04%, presisi 95.84%, recall 94.12%, F1 94.97%, serta deteksi halusinasi 87.63% dengan false alarm 8.91% dan latensi 3.2 token.</t>
+          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Model mencapai akurasi 95.04% dan F1 94.97%, mengungguli baseline AraELECTRA dan mBERT-RAG, serta mendeteksi halusinasi dengan tingkat 87.63% dan kegagalan hanya 8.91%.</t>
+          <t>Optimasi retrieval terbukti penting; peningkatan recall dan precision meningkatkan kualitas jawaban, sementara LLM cenderung memberikan jawaban meski dokumen relevan tidak ada, terutama pada model kecil.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
+          <t>Penulis mengakui kurangnya investigasi sistematis pada tiap komponen RAG dan bahwa studi terbatas pada data internal serta bahasa Inggris, sehingga generalisasi masih terbatas.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun berhasil mengurangi halusinasi pada RAG bahasa Arab, penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zhao, Y., Singh, P., Bhathena, H., et al. (2024). Optimizing LLM Based Retrieval Augmented Generation Pipelines in the Financial Domain. NAACL 2024 Industry Track, 279-294. https://doi.org/10.18653/v1/2024.naacl-industry.23</t>
+          <t>Chen, J., Zhou, P., Hua, Y., et al. (2024). FinTextQA: A Dataset for Long-form Financial Question Answering. ACL 2024 (Long Papers), 6025-6047. https://doi.org/10.18653/v1/2024.acl-long.328</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
+          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Studi menggunakan dua dataset RAG dari sektor perbankan: halaman web publik tentang produk perbankan dan panduan kebijakan internal, keduanya berbahasa Inggris.</t>
+          <t>Dataset berfokus pada domain keuangan, mencakup dokumen teks buku, regulasi, dan kebijakan dari sumber seperti HKMA, EU, dan Federal Reserve; berisi 1.262 pasangan QA dalam bahasa Inggris.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
+          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
+          <t>Evaluasi menggunakan metrik otomatis ROUGE-1/2/L, BLEU, serta skor GPT-4 yang menilai kegunaan, relevansi, akurasi, kedalaman, dan kreativitas; juga melibatkan penilaian manusia dengan skala 1-5.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Optimasi retrieval terbukti penting; peningkatan recall dan precision meningkatkan kualitas jawaban, sementara LLM cenderung memberikan jawaban meski dokumen relevan tidak ada, terutama pada model kecil.</t>
+          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Penulis mengakui kurangnya investigasi sistematis pada tiap komponen RAG dan bahwa studi terbatas pada data internal serta bahasa Inggris, sehingga generalisasi masih terbatas.</t>
+          <t>Dataset memiliki jumlah pasangan QA yang relatif kecil dibandingkan dataset AI-generated besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh karena hak cipta; belum ada dataset LFQA khusus untuk bahasa Indonesia.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
+          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chen, J., Zhou, P., Hua, Y., et al. (2024). FinTextQA: A Dataset for Long-form Financial Question Answering. ACL 2024 (Long Papers), 6025-6047. https://doi.org/10.18653/v1/2024.acl-long.328</t>
+          <t>Iaroshev, I., Pillai, R., Vaglietti, L., et al. (2024). Evaluating Retrieval-Augmented Generation Models for Financial Report Question and Answering. Applied Sciences 14(20), 9318. https://doi.org/10.3390/app14209318</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
+          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dataset berfokus pada domain keuangan, mencakup dokumen teks buku, regulasi, dan kebijakan dari sumber seperti HKMA, EU, dan Federal Reserve; berisi 1.262 pasangan QA dalam bahasa Inggris.</t>
+          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
+          <t>Sistem RAG menggunakan retriever OpenAI ADA, embedder MiniLM pada model tiga, dan generator OpenAI GPT-4; variasi komponen diuji dalam beberapa model.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik otomatis ROUGE-1/2/L, BLEU, serta skor GPT-4 yang menilai kegunaan, relevansi, akurasi, kedalaman, dan kreativitas; juga melibatkan penilaian manusia dengan skala 1-5.</t>
+          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
+          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dataset memiliki jumlah pasangan QA yang relatif kecil dibandingkan dataset AI-generated besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh karena hak cipta; belum ada dataset LFQA khusus untuk bahasa Indonesia.</t>
+          <t>tidak disebut</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Iaroshev, I., Pillai, R., Vaglietti, L., et al. (2024). Evaluating Retrieval-Augmented Generation Models for Financial Report Question and Answering. Applied Sciences 14(20), 9318. https://doi.org/10.3390/app14209318</t>
+          <t>Lithgow-Serrano, O., Kletz, D., Kanjirangat, V., et al. (2025). Assessing RAG System Capabilities on Financial Documents. FinNLP 2025, 124-147. https://doi.org/10.18653/v1/2025.finnlp-2.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
+          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
+          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever OpenAI ADA, embedder MiniLM pada model tiga, dan generator OpenAI GPT-4; variasi komponen diuji dalam beberapa model.</t>
+          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
+          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
+          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
+          <t>Penulis mencatat keterbatasan LLM dalam penalaran kuantitatif, cakupan dokumen yang hanya sebagian dari keseluruhan domain, serta metrik yang belum sepenuhnya menangkap semua dimensi kualitas jawaban.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
+          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wang, S., Tan, J., Dou, Z., &amp; Wen, J.-R. (2025). OmniEval: An Omnidirectional and Automatic RAG Evaluation Benchmark in Financial Domain. EMNLP 2025, 5726-5751. https://doi.org/10.18653/v1/2025.emnlp-main.292</t>
+          <t>Choi, C., Kwon, J., Ha, J., et al. (2025). FinDER: Financial Dataset for Question Answering and Evaluating Retrieval-Augmented Generation. ACM ICAIF '25. https://doi.org/10.1145/3768292.3770361</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan benchmark RAG yang komprehensif karena benchmark saat ini memiliki skenario sempit dan dimensi evaluasi terbatas.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Domain keuangan mencakup subdomain seperti perbankan investasi, asuransi, pasar modal, dan lainnya, dengan dokumen berbahasa Mandarin/Chinese yang diambil dari situs resmi dan berbagai format.</t>
+          <t>Dataset FINDER mencakup dokumen keuangan seperti artikel berita, filing, dan basis pengetahuan, berfokus pada bahasa Inggris dan tidak menyebutkan dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Menggunakan retriever seperti BGE-M3, BGE-large-zh, GTE-Qwen2-1.5b, dan jina-zh; generator LLM termasuk Qwen2.5-72B, Deepseek-v2-chat, Yi15-34B, Llama3.1-70B; chunking panjang 2048 dengan overlap 256.</t>
+          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik multi-aspek seperti ACC, HAL (hallucination), NAC (numerical accuracy), Rouge-L, serta MRR dan MAP untuk retriever.</t>
+          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GTE-Qwen2-1.5B menunjukkan performa retrieval terbaik pada sebagian besar metrik; performa RAG bervariasi antar topik dan tugas, dan masih terdapat ruang besar untuk perbaikan.</t>
+          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Keterbatasan meliputi kegagalan retriever pada topik ekor panjang, kegagalan generator dalam perhitungan keuangan, serta distribusi data yang masih terbatas dan berpotensi bias.</t>
+          <t>Penulis mencatat bahwa dataset sebelumnya tidak mencerminkan ambiguitas kueri dan proses retrieval yang penting untuk QA keuangan.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Inferensi: Paper tidak mengevaluasi kemampuan abstention atau faithfulness pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak mencakup fokus riset yang diinginkan.</t>
+          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lithgow-Serrano, O., Kletz, D., Kanjirangat, V., et al. (2025). Assessing RAG System Capabilities on Financial Documents. FinNLP 2025, 124-147. https://doi.org/10.18653/v1/2025.finnlp-2.9</t>
+          <t>Ngartera, L., Nadarajah, S., &amp; Koina, R. (2026). Bayesian RAG: Uncertainty-Aware Retrieval for Reliable Financial Question Answering. Frontiers in Artificial Intelligence 8, 1668172. https://doi.org/10.3389/frai.2025.1668172</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
+          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
+          <t>Fokus pada analisis dokumen keuangan regulasi berbahasa Inggris, menggunakan dataset seperti FinanceBench dengan dokumen laporan tahunan perusahaan.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
+          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
+          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
+          <t>Bayesian RAG meningkatkan faithfulness menjadi 0.87, menurunkan hallucination menjadi 0.13, dan memberikan kenaikan akurasi 25% dengan overhead latency 33 ms.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Penulis mencatat keterbatasan LLM dalam penalaran kuantitatif, cakupan dokumen yang hanya sebagian dari keseluruhan domain, serta metrik yang belum sepenuhnya menangkap semua dimensi kualitas jawaban.</t>
+          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Choi, C., Kwon, J., Ha, J., et al. (2025). FinDER: Financial Dataset for Question Answering and Evaluating Retrieval-Augmented Generation. ACM ICAIF '25. https://doi.org/10.1145/3768292.3770361</t>
+          <t>Sarmah, B., Mehta, D. B., Hall, B., et al. (2024). HybridRAG: Integrating Knowledge Graphs and Vector Retrieval Augmented Generation for Efficient Information Extraction. ACM ICAIF '24. https://doi.org/10.1145/3677052.3698671</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
+          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dataset FINDER mencakup dokumen keuangan seperti artikel berita, filing, dan basis pengetahuan, berfokus pada bahasa Inggris dan tidak menyebutkan dokumen perbankan Indonesia.</t>
+          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
+          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
+          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
+          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Penulis mencatat bahwa dataset sebelumnya tidak mencerminkan ambiguitas kueri dan proses retrieval yang penting untuk QA keuangan.</t>
+          <t>GraphRAG kurang baik pada tugas Q&amp;A abstraktif dan ketika entitas tidak eksplisit; tantangan pada konteks panjang dan kualitas konteks yang tidak konsisten.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
+          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zhao, S., Jin, Z., Li, S., &amp; Gao, J. (2025). FinRAGBench-V: A Benchmark for Multimodal RAG with Visual Citation in the Financial Domain. EMNLP 2025, 4215-4249. https://doi.org/10.18653/v1/2025.emnlp-main.211</t>
+          <t>Wang, X., Chi, J., Tai, Z., et al. (2025). FinSage: A Multi-aspect RAG System for Financial Filings Question Answering. CIKM '25, 6144-6152. https://doi.org/10.1145/3746252.3761587</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Membangun benchmark FinRAGBench-V dan baseline RGenCite untuk RAG multimodal dengan visual citation.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Domain keuangan, mencakup laporan riset, laporan keuangan, prospektus, makalah akademik, dan majalah finansial; data dikumpulkan dari Qianzhan.com, FinGLM, BSCF, jurnal, dan Financial Times; ukuran besar dan berbahasa Inggris serta Mandarin.</t>
+          <t>Sistem diuji pada FinanceBench, dataset QA keuangan berbahasa Inggris dengan 150 pertanyaan tentang perusahaan publik, serta dokumen filing SEC.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Menggunakan retriever teksual (Jina-ColBERT-V2, Multilingual-E5-large) dan multimodal (ColQwen2, GME-Qwen2-VL-2B, DSE-QWen2-2b-MRL-V1); chunking pada level halaman; generator memakai MLLM seperti GPT-4o, GPT-4V, Gemini-2.0-Flash, Qwen2.5-VL-72B-Instruct; visual citation diintegrasikan pada tahap generasi.</t>
+          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup retrieval (nDCG@k, Recall@k, MRR@k), akurasi jawaban (ROUGE, ACC), serta kualitas visual citation (precision, recall pada level halaman dan blok, IoU, dan penilaian manusia 0-5).</t>
+          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Multimodal retriever mencapai recall@10 hingga 90.13 % (Chinese) dan 85.86 % (English), jauh di atas retriever teksual (42.71 %/36.36 %). Visual citation dengan image-cropping memperoleh korelasi Pearson 65.06 dengan IoU dan 68.01 dengan penilaian manusia.</t>
+          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tidak melatih model khusus multimodal RAG untuk domain keuangan; benchmark berbahasa Inggris dan Mandarin, tidak mencakup bahasa Indonesia; belum mengatasi kebutuhan abstention.</t>
+          <t>Penulis mencatat kesulitan integrasi RAG ke dalam tugas kepatuhan keuangan karena keterbatasan domain dan tantangan multi-modalitas.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Penulis menyatakan belum melatih model khusus untuk RAG multimodal keuangan dan benchmark berbahasa Inggris/Mandarin, sehingga tidak mencakup dokumen perbankan berbahasa Indonesia atau evaluasi abstention. Inferensi: Karena tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia, gap penelitian tetap ada.</t>
+          <t>Inferensi: Meskipun FinSage meningkatkan akurasi dan recall pada dokumen filing berbahasa Inggris, tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga masih ada celah untuk menilai keandalan sistem RAG dalam konteks bahasa dan domain tersebut.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ngartera, L., Nadarajah, S., &amp; Koina, R. (2026). Bayesian RAG: Uncertainty-Aware Retrieval for Reliable Financial Question Answering. Frontiers in Artificial Intelligence 8, 1668172. https://doi.org/10.3389/frai.2025.1668172</t>
+          <t>Katerenchuk, D., Duboue, P., Evanini, K., et al. (2026). FinRAG-12B: A Production-Validated Recipe for Grounded Question Answering in Banking. arXiv:2605.05482. https://doi.org/10.48550/arXiv.2605.05482</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
+          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fokus pada analisis dokumen keuangan regulasi berbahasa Inggris, menggunakan dataset seperti FinanceBench dengan dokumen laporan tahunan perusahaan.</t>
+          <t>tidak disebut</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
+          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
+          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bayesian RAG meningkatkan faithfulness menjadi 0.87, menurunkan hallucination menjadi 0.13, dan memberikan kenaikan akurasi 25% dengan overhead latency 33 ms.</t>
+          <t>FinRAG-12B meningkatkan resolution rate sebesar 7.1 poin persentase, mencapai F1 0.284 pada FinanceBench dengan tingkat kutipan 97.3%, serta menurunkan tingkat penolakan yang tidak tepat.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
+          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sarmah, B., Mehta, D. B., Hall, B., et al. (2024). HybridRAG: Integrating Knowledge Graphs and Vector Retrieval Augmented Generation for Efficient Information Extraction. ACM ICAIF '24. https://doi.org/10.1145/3677052.3698671</t>
+          <t>Gondhalekar, C., Patel, U., &amp; Yeh, F.-C. (2025). MultiFinRAG: An Optimized Multimodal Retrieval-Augmented Generation Framework for Financial Question Answering. IEEE International Conference on Big Data (BigData) 2025. https://doi.org/10.1109/bigdata66926.2025.11401444</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
+          <t>Masalahnya adalah mengevaluasi output LLM pada dokumen keuangan multimodal dengan metrik yang tepat.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
+          <t>Dataset terdiri dari 300 pertanyaan QA yang dibuat dari dokumen keuangan SEC seperti Form 10-K, 10-Q, 8-K, dan DEF 14A, semuanya berbahasa Inggris.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
+          <t>MultiFinRAG menggunakan ekstraksi multimodal, embedding dengan threshold kesamaan modalitas, dan strategi fallback bertingkat dari teks ke tabel/gambar, serta DPR sebagai retriever.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
+          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
+          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>GraphRAG kurang baik pada tugas Q&amp;A abstraktif dan ketika entitas tidak eksplisit; tantangan pada konteks panjang dan kualitas konteks yang tidak konsisten.</t>
+          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
+          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wang, X., Chi, J., Tai, Z., et al. (2025). FinSage: A Multi-aspect RAG System for Financial Filings Question Answering. CIKM '25, 6144-6152. https://doi.org/10.1145/3746252.3761587</t>
+          <t>Cheng, Z., Lai, L., &amp; Liu, Y. (2026). Sustainable Hybrid Document-Routed Retrieval for Financial RAG: Resolving the Robustness-Precision Trade-off. Intelligent Systems with Applications 32, 200720. https://doi.org/10.1016/j.iswa.2026.200720</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
+          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sistem diuji pada FinanceBench, dataset QA keuangan berbahasa Inggris dengan 150 pertanyaan tentang perusahaan publik, serta dokumen filing SEC.</t>
+          <t>Domain keuangan, menggunakan benchmark FinDER dengan 1.500 kueri pada lima grup; tipe dokumen regulasi, ukuran tidak disebut, bahasa tidak disebut.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
+          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
+          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
+          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Penulis mencatat kesulitan integrasi RAG ke dalam tugas kepatuhan keuangan karena keterbatasan domain dan tantangan multi-modalitas.</t>
+          <t>tidak disebut</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinSage meningkatkan akurasi dan recall pada dokumen filing berbahasa Inggris, tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga masih ada celah untuk menilai keandalan sistem RAG dalam konteks bahasa dan domain tersebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cho, E., Lee, Y., Kim, M., et al. (2026). K-FinHallu: A Hallucination Detection Benchmark for Multi-Turn RAG in Korean Finance. arXiv:2605.29523. https://doi.org/10.48550/arXiv.2605.29523</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Paper ini mengatasi masalah mendeteksi hallucination intrinsik pada sistem RAG multi-turn di domain keuangan Korea dengan fokus pada kesetiaan sumber.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Domainnya adalah keuangan Korea; menggunakan dataset “Korean Financial and Legal Document Machine Reading Comprehension” yang berisi dokumen keuangan dan hukum berbahasa Korea.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Pipeline otomatis menghasilkan split pelatihan; model generator 8B di-fine-tune dengan supervisi rasional, menggunakan embedding KURE Korean untuk chunking, dan retriever berbasis dokumen sumber.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan klasifikasi biner (akurasi, presisi, recall, F1) serta klasifikasi empat kelas yang mencakup kemampuan menolak (refusal) dalam dialog multi-turn.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Model tertutup Gemini-2.5-Flash mencapai F1 tertinggi 0.860; abstention tetap menjadi aspek terlemah pada semua model yang diuji.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Abstention yang tepat masih paling lemah; temuan terbatas pada bahasa Korea sehingga transferabilitas ke bahasa atau yurisdiksi lain terbatas.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun menyediakan benchmark RAG multi-turn untuk bahasa Korea, penelitian ini tidak mencakup bahasa Indonesia atau dokumen produk perbankan, sehingga belum mengevaluasi faithfulness dan abstention pada konteks Indonesia. Penulis juga mencatat bahwa temuan mereka terbatas pada bahasa Korea, sehingga transferabilitas ke bahasa lain tidak dijamin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Katerenchuk, D., Duboue, P., Evanini, K., et al. (2026). FinRAG-12B: A Production-Validated Recipe for Grounded Question Answering in Banking. arXiv:2605.05482. https://doi.org/10.48550/arXiv.2605.05482</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>FinRAG-12B meningkatkan resolution rate sebesar 7.1 poin persentase, mencapai F1 0.284 pada FinanceBench dengan tingkat kutipan 97.3%, serta menurunkan tingkat penolakan yang tidak tepat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Gondhalekar, C., Patel, U., &amp; Yeh, F.-C. (2025). MultiFinRAG: An Optimized Multimodal Retrieval-Augmented Generation Framework for Financial Question Answering. IEEE International Conference on Big Data (BigData) 2025. https://doi.org/10.1109/bigdata66926.2025.11401444</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Masalahnya adalah mengevaluasi output LLM pada dokumen keuangan multimodal dengan metrik yang tepat.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Dataset terdiri dari 300 pertanyaan QA yang dibuat dari dokumen keuangan SEC seperti Form 10-K, 10-Q, 8-K, dan DEF 14A, semuanya berbahasa Inggris.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MultiFinRAG menggunakan ekstraksi multimodal, embedding dengan threshold kesamaan modalitas, dan strategi fallback bertingkat dari teks ke tabel/gambar, serta DPR sebagai retriever.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cheng, Z., Lai, L., &amp; Liu, Y. (2026). Sustainable Hybrid Document-Routed Retrieval for Financial RAG: Resolving the Robustness-Precision Trade-off. Intelligent Systems with Applications 32, 200720. https://doi.org/10.1016/j.iswa.2026.200720</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Domain keuangan, menggunakan benchmark FinDER dengan 1.500 kueri pada lima grup; tipe dokumen regulasi, ukuran tidak disebut, bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
           <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Liu, Y., Shangguan, J., Wang, Q., &amp; Xu, S. (2026). MacroRisk-agent: A Retrieval-Augmented Multi-Agent Framework with Deterministic Validation Gates for Auditable Stress Testing. Scientific Reports. https://doi.org/10.1038/s41598-026-73453-3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Makalah mengidentifikasi tiga tantangan utama LLM multi-agent dalam keputusan berisiko tinggi: kontrol halusinasi, penggabungan penalaran semantik dengan simulasi numerik deterministik, serta auditabilitas end-to-end.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Kerangka diuji pada domain stress testing keuangan menggunakan dataset publik (FRED, Yahoo Finance), perpustakaan 150 peristiwa krisis, dan 10 portofolio institusional sintetis.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent memperkenalkan pipeline retrieval-augmented generation dengan deterministic validation gates yang mengubah intent stres bahasa alami menjadi objek parameter ber-skema.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup tingkat validitas 92.6% vs 78.4% (p&lt;0.001), peningkatan estimasi kerugian sistemik 52%, dan tingkat keberhasilan keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent mencapai validitas 92.6% (lebih tinggi 14.2 poin persentase), menghasilkan estimasi kerugian sistemik 52% lebih tinggi, dan sukses keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Validasi pada data institusional nyata belum dilakukan; penelitian masih bersifat proof-of-concept pada data sintetis dan publik.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Penulis tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia; mereka hanya menguji pada dataset publik berbahasa Inggris dan data sintetis. Inferensi: Oleh karena itu, belum ada analisis tentang bagaimana RAG menangani konteks bahasa Indonesia atau menolak menjawab bila konteks tidak memadai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Beauchemin, D., &amp; Khoury, R. (2026). A Human-Centric Evaluation of a Retrieval-Augmented Generation System for Explaining Quebec Insurance Contracts. HCI International 2026 Posters (CCIS), 151-168. https://doi.org/10.1007/978-3-032-30826-9_15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi sistem RAG yang menjelaskan kontrak asuransi Quebec dengan fokus pada pengalaman pengguna secara manusiawi.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Domainnya adalah asuransi kendaraan di Quebec, menggunakan dataset percakapan 3.759 pasangan pesan-jawaban dari 154 peserta yang mayoritas berbahasa Prancis.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sistem menggunakan model LLM OpenAI “o3-2025-04-16” dengan arsitektur RAG standar, namun detail retriever dan strategi chunking tidak dijelaskan.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup survei Likert 7-point, analisis statistik t-test, Kruskal-Wallis, dan korelasi Pearson untuk mengukur kepuasan, usaha kognitif, dan kepercayaan.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pengguna dengan literasi rendah melaporkan kepuasan secara signifikan lebih tinggi, sementara manfaat inti sistem diakui secara universal oleh semua kelompok.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Penulis mencatat adanya kesalahan faktual, preferensi pengguna terhadap agen manusia, serta keterbatasan generalisasi karena sampel berpendidikan tinggi dan setting eksperimental.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention RAG pada dokumen perbankan berbahasa Indonesia; fokusnya terbatas pada konteks asuransi Quebec berbahasa Prancis. Inferensi: Karena tidak ada pengujian terhadap keakuratan faktual atau penolakan ketika konteks tidak memadai, gap muncul untuk aplikasi bahasa Indonesia di domain perbankan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Luketina, M., Benkel, A., &amp; Schuetz, C. G. (2026). Using Large Language Models for Legal Decision-Making in Austrian Value-Added Tax Law: A Comparative Study. Journal of Business Analytics, 1-25. https://doi.org/10.1080/2573234x.2026.2720626</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi dua pendekatan peningkatan performa LLM, yaitu fine-tuning dan retrieval-augmented generation (RAG), untuk mendukung pengambilan keputusan hukum dalam konteks pajak pertambahan nilai (VAT).</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Domainnya adalah pajak nilai tambah (VAT) di Austria/EU, menggunakan kasus VAT dari buku teks serta kasus nyata dari firma konsultan pajak; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LLM yang dikonfigurasi dengan tepat dapat secara efektif mendukung profesional pajak dalam tugas-tugas VAT, mengotomatisasi pekerjaan rutin, dan menghasilkan justifikasi hukum yang kuat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Prototipe belum siap untuk otomatisasi penuh karena sensitivitas domain hukum, serta masih terdapat keterbatasan dalam menangani pengetahuan implisit klien dan dokumentasi kontekstual.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Inferensi: Makalah ini tidak membahas faithfulness atau abstention pada sistem RAG, tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga tidak menjawab fokus penelitian yang menilai kemampuan RAG dalam konteks tersebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Schmitt, K., Vial, G., &amp; Blohm, I. (2026). Alpes Bank's Journey to Creating Value at Scale with Generative AI. Journal of Information Technology Teaching Cases, 20438869261460075. https://doi.org/10.1177/20438869261460075</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi peluncuran pilot GenAI "no-regret" dalam satu kuartal untuk meningkatkan nilai pada Alpes Bank.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Studi kasus pada Alpes Bank, bank universal Swiss, menggunakan email inquiry sebagai data; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Tim membangun email assistant berbasis retrieval-augmented generation (RAG) bekerja sama dengan AILabs; detail teknis tidak disebut.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan dengan mengukur pengurangan waktu penanganan inquiry rutin, tercatat penurunan 21%.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Email assistant berbasis GenAI mengurangi waktu penanganan inquiry rutin sebesar 21%.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Inferensi: Penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak menjawab fokus riset yang diusulkan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Opin, S. A. I., Thakur, R. A., Raiyan, A. K., et al. (2025). NextRAG: A Bilingual Retrieval-Augmented Generation Framework for Financial Question-Answering. 28th International Conference on Computer and Information Technology (ICCIT 2025), 3604-3609. IEEE. https://doi.org/10.1109/iccit68739.2025.11491522</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Penelitian ini memperkenalkan NextRAG, kerangka Retrieval-Augmented Generation bilingual untuk meningkatkan penelusuran pengetahuan keuangan dan menjawab pertanyaan.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fokus pada dokumen keuangan multibahasa dari institusi dan regulator di Bangladesh, serta dataset Q&amp;A keuangan bilingual yang beragam.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Menggunakan retrieval sparse BM25 dengan smoothing Dirichlet, fusi Reciprocal Rank Fusion, re-ranking cross-encoder, serta prompting yang sadar bahasa untuk Bangla dan Inggris.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Dievaluasi pada dataset Q&amp;A bilingual dengan metrik mean cosine similarity dan F1 score, membandingkan dengan RAG konvensional.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NextRAG secara konsisten mengungguli RAG konvensional, memperoleh mean cosine similarity 0.77 dan F1 68.3%.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun NextRAG menangani dokumen bilingual, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diinginkan.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1987,7 +1564,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2002,24 +1579,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Penelitian ini mengatasi masalah halusinasi pada sistem Retrieval-Augmented Generation (RAG) bahasa Arab untuk analisis dokumen keuangan.</t>
+          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>This research introduces a customized attention visualization framework for mitigating hallucinations in Arabic Retrieval-Augmented Generation (RAG) systems tailored for financial document analysis.</t>
+          <t>We comprehensively assess various factors that contribute to the answer generation quality in LLM RAG systems, ranging from sensitivity to retrieval quality to the impact of different prompts</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2029,29 +1606,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Domain keuangan, dokumen finansial berbahasa Arab, dengan dataset baru berisi 7.000 pasangan query-konteks beranotasi.</t>
+          <t>Studi menggunakan dua dataset RAG dari sektor perbankan: halaman web publik tentang produk perbankan dan panduan kebijakan internal, keduanya berbahasa Inggris.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trained on a newly constructed dataset of 7,000 annotated Arabic financial query-context pairs</t>
+          <t>Banking webpages: Public webpages with general information on banking products, and Banking policy guides: internal guides for customer service executives</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:0; P04:pdf:1; P04:pdf:4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2066,24 +1643,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Metode memperluas MarBERT dengan mekanisme supervisi perhatian dua tahap dan loss yang sadar halusinasi, serta ambang presisi dinamis untuk penolakan output.</t>
+          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The proposed architecture extends MarBERT with a dual-stage attention supervision mechanism and a hallucination-aware loss formulation</t>
+          <t>We sampled 800 user queries for each dataset and obtained retrieved document chunks using a retriever(OpenAI Embeddings2)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:12; P04:pdf:29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2098,24 +1675,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan akurasi klasifikasi 95.04%, presisi 95.84%, recall 94.12%, F1 94.97%, serta deteksi halusinasi 87.63% dengan false alarm 8.91% dan latensi 3.2 token.</t>
+          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>classification accuracy, 95.84% precision, 94.12% recall, and an F1 score of 94.97%... detection rate with only 8.91% false alarms and a detection latency of 3.2 tokens</t>
+          <t>Our findings reveal that generative LLMs outperform baseline models in answer quality, even on metrics emphasizing extractiveness</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>P03:abstract:1; P03:abstract:0</t>
+          <t>P04:pdf:7; P04:pdf:29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2130,24 +1707,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Model mencapai akurasi 95.04% dan F1 94.97%, mengungguli baseline AraELECTRA dan mBERT-RAG, serta mendeteksi halusinasi dengan tingkat 87.63% dan kegagalan hanya 8.91%.</t>
+          <t>Optimasi retrieval terbukti penting; peningkatan recall dan precision meningkatkan kualitas jawaban, sementara LLM cenderung memberikan jawaban meski dokumen relevan tidak ada, terutama pada model kecil.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>outperforming AraELECTRA and mBERT-RAG baselines... reaches an 87.63% detection rate with only 8.91% false alarms</t>
+          <t>We recommend prioritizing retrieval recall, while tuning retrieval systems, as LLMs exhibit pseudo-helpfulness when relevant gold document(s) are not retrieved</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>P03:abstract:1; P03:abstract:0</t>
+          <t>P04:pdf:30; P04:pdf:29; P04:pdf:22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,21 +1734,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>Penulis mengakui kurangnya investigasi sistematis pada tiap komponen RAG dan bahwa studi terbatas pada data internal serta bahasa Inggris, sehingga generalisasi masih terbatas.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>there is a lack of systematic investigations of the impact of each component (retriever, prompts, models) on answer generation quality</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>P04:pdf:2; P04:pdf:9; P04:pdf:4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2186,24 +1771,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun berhasil mengurangi halusinasi pada RAG bahasa Arab, penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arabic Retrieval-Augmented Generation (RAG) systems</t>
+          <t>LLMs tend to provide answers even when relevant source information is missing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:7; P04:pdf:0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2218,24 +1803,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
+          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>We comprehensively assess various factors that contribute to the answer generation quality in LLM RAG systems, ranging from sensitivity to retrieval quality to the impact of different prompts</t>
+          <t>introducing the first LFQA financial dataset and conducting comprehensive benchmark experiments</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>P04:pdf:9</t>
+          <t>P05:pdf:10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,24 +1835,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Studi menggunakan dua dataset RAG dari sektor perbankan: halaman web publik tentang produk perbankan dan panduan kebijakan internal, keduanya berbahasa Inggris.</t>
+          <t>Dataset berfokus pada domain keuangan, mencakup dokumen teks buku, regulasi, dan kebijakan dari sumber seperti HKMA, EU, dan Federal Reserve; berisi 1.262 pasangan QA dalam bahasa Inggris.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Banking webpages: Public webpages with general information on banking products, and Banking policy guides: internal guides for customer service executives</t>
+          <t>FinTextQA contains 1,262 QA pairs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>P04:pdf:0; P04:pdf:1; P04:pdf:4</t>
+          <t>P05:pdf:5; P05:pdf:16; P05:pdf:4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2282,24 +1867,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
+          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>We sampled 800 user queries for each dataset and obtained retrieved document chunks using a retriever(OpenAI Embeddings2)</t>
+          <t>We adopt four popular embedding models... We explore three retriever methods... examine the influence of three rerankers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>P04:pdf:12; P04:pdf:29</t>
+          <t>P05:pdf:14; P05:pdf:28; P05:pdf:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2314,24 +1899,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
+          <t>Evaluasi menggunakan metrik otomatis ROUGE-1/2/L, BLEU, serta skor GPT-4 yang menilai kegunaan, relevansi, akurasi, kedalaman, dan kreativitas; juga melibatkan penilaian manusia dengan skala 1-5.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Our findings reveal that generative LLMs outperform baseline models in answer quality, even on metrics emphasizing extractiveness</t>
+          <t>ROUGE and BLEU are used to automatically measure... GPT‑4 scoring method is used to evaluate the answers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>P04:pdf:7; P04:pdf:29</t>
+          <t>P05:pdf:38; P05:pdf:19; P05:pdf:37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2346,24 +1931,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optimasi retrieval terbukti penting; peningkatan recall dan precision meningkatkan kualitas jawaban, sementara LLM cenderung memberikan jawaban meski dokumen relevan tidak ada, terutama pada model kecil.</t>
+          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>We recommend prioritizing retrieval recall, while tuning retrieval systems, as LLMs exhibit pseudo-helpfulness when relevant gold document(s) are not retrieved</t>
+          <t>Ada2, achieving a score of 4.586... AMR outperforms the rest with an impressive score of 4.492... ROUGE‑1 scores are 0.317 and 0.270, respectively; the GPT‑4 scores are 4.238 and 4.293</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>P04:pdf:30; P04:pdf:29; P04:pdf:22</t>
+          <t>P05:pdf:39; P05:pdf:40; P05:pdf:46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2373,29 +1958,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Penulis mengakui kurangnya investigasi sistematis pada tiap komponen RAG dan bahwa studi terbatas pada data internal serta bahasa Inggris, sehingga generalisasi masih terbatas.</t>
+          <t>Dataset memiliki jumlah pasangan QA yang relatif kecil dibandingkan dataset AI-generated besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh karena hak cipta; belum ada dataset LFQA khusus untuk bahasa Indonesia.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>there is a lack of systematic investigations of the impact of each component (retriever, prompts, models) on answer generation quality</t>
+          <t>FinTextQA contains a relatively smaller number of QA pairs... High‑quality data are challenging to acquire... none of them addresses LFQA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>P04:pdf:2; P04:pdf:9; P04:pdf:4</t>
+          <t>P05:pdf:49; P05:pdf:10; P05:pdf:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2410,24 +1995,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
+          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LLMs tend to provide answers even when relevant source information is missing</t>
+          <t>none of them addresses LFQA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>P04:pdf:7; P04:pdf:0</t>
+          <t>P05:pdf:12; P05:pdf:4; P05:pdf:11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2442,24 +2027,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
+          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>introducing the first LFQA financial dataset and conducting comprehensive benchmark experiments</t>
+          <t>This study explores the application of retrieval-augmented generation (RAG) to improve the accuracy and reliability of large language models (LLMs) in the context of financial report analysis.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>P05:pdf:10</t>
+          <t>P06:abstract:0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2469,29 +2054,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Dataset berfokus pada domain keuangan, mencakup dokumen teks buku, regulasi, dan kebijakan dari sumber seperti HKMA, EU, dan Federal Reserve; berisi 1.262 pasangan QA dalam bahasa Inggris.</t>
+          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FinTextQA contains 1,262 QA pairs</t>
+          <t>enhancing the question-and-answering capabilities regarding the half-yearly or quarterly financial reports of banks.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>P05:pdf:5; P05:pdf:16; P05:pdf:4</t>
+          <t>P06:abstract:0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2506,24 +2091,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
+          <t>Sistem RAG menggunakan retriever OpenAI ADA, embedder MiniLM pada model tiga, dan generator OpenAI GPT-4; variasi komponen diuji dalam beberapa model.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>We adopt four popular embedding models... We explore three retriever methods... examine the influence of three rerankers</t>
+          <t>model one (OpenAI ADA and OpenAI GPT-4) achieved the highest performance</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>P05:pdf:14; P05:pdf:28; P05:pdf:31</t>
+          <t>P06:abstract:0; P06:abstract:1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2538,24 +2123,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik otomatis ROUGE-1/2/L, BLEU, serta skor GPT-4 yang menilai kegunaan, relevansi, akurasi, kedalaman, dan kreativitas; juga melibatkan penilaian manusia dengan skala 1-5.</t>
+          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ROUGE and BLEU are used to automatically measure... GPT‑4 scoring method is used to evaluate the answers</t>
+          <t>showing robust accuracy and relevance in response</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>P05:pdf:38; P05:pdf:19; P05:pdf:37</t>
+          <t>P06:abstract:1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2570,24 +2155,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
+          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ada2, achieving a score of 4.586... AMR outperforms the rest with an impressive score of 4.492... ROUGE‑1 scores are 0.317 and 0.270, respectively; the GPT‑4 scores are 4.238 and 4.293</t>
+          <t>Model three (MiniLM Embedder and OpenAI GPT-4) scored significantly lower, indicating the importance of high-quality components.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>P05:pdf:39; P05:pdf:40; P05:pdf:46</t>
+          <t>P06:abstract:1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2597,29 +2182,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dataset memiliki jumlah pasangan QA yang relatif kecil dibandingkan dataset AI-generated besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh karena hak cipta; belum ada dataset LFQA khusus untuk bahasa Indonesia.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>FinTextQA contains a relatively smaller number of QA pairs... High‑quality data are challenging to acquire... none of them addresses LFQA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>P05:pdf:49; P05:pdf:10; P05:pdf:12</t>
-        </is>
-      </c>
+          <t>tidak disebut</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2634,24 +2211,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>none of them addresses LFQA</t>
+          <t>aim is to enhance context relevance, answer faithfulness, and answer relevance</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>P05:pdf:12; P05:pdf:4; P05:pdf:11</t>
+          <t>P06:abstract:0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2666,24 +2243,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
+          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>This study explores the application of retrieval-augmented generation (RAG) to improve the accuracy and reliability of large language models (LLMs) in the context of financial report analysis.</t>
+          <t>These insights emphasize the importance of benchmarks that capture real-world document heterogeneity while enabling multifaceted evaluations aligned with the strengths and trade-offs of both models and methodologies.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>P06:abstract:0</t>
+          <t>P08:pdf:12; P08:pdf:8; P08:pdf:11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2693,29 +2270,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
+          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enhancing the question-and-answering capabilities regarding the half-yearly or quarterly financial reports of banks.</t>
+          <t>FinDoc-RAG comprises 600+ QA pairs extracted from 46 documents in English from UBS AG and other UBS entities.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>P06:abstract:0</t>
+          <t>P08:pdf:5; P08:pdf:7; P08:pdf:4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2730,24 +2307,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever OpenAI ADA, embedder MiniLM pada model tiga, dan generator OpenAI GPT-4; variasi komponen diuji dalam beberapa model.</t>
+          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>model one (OpenAI ADA and OpenAI GPT-4) achieved the highest performance</t>
+          <t>Vector-based (Vector-RAG) ... using cosine as the similarity metric.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>P06:abstract:0; P06:abstract:1</t>
+          <t>P08:pdf:50; P08:pdf:27; P08:pdf:25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2762,24 +2339,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
+          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>showing robust accuracy and relevance in response</t>
+          <t>We computed accuracy as the mean proportion of CORRECT responses per question ... adopt the LLMLogScore (L3Score) metric.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>P06:abstract:1</t>
+          <t>P08:pdf:22; P08:pdf:36; P08:pdf:35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2789,29 +2366,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
+          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Model three (MiniLM Embedder and OpenAI GPT-4) scored significantly lower, indicating the importance of high-quality components.</t>
+          <t>leading systems achieve 0.91 accuracy in factual extraction but only 0.44 on multi-document synthesis tasks.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>P06:abstract:1</t>
+          <t>P08:pdf:12; P08:pdf:26; P08:pdf:40</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2821,21 +2398,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>Penulis mencatat keterbatasan LLM dalam penalaran kuantitatif, cakupan dokumen yang hanya sebagian dari keseluruhan domain, serta metrik yang belum sepenuhnya menangkap semua dimensi kualitas jawaban.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Current LLMs show limitations in quantitative reasoning and cross-document synthesis essential for financial applications.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>P08:pdf:2; P08:pdf:49; P08:pdf:6</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2850,24 +2435,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
+          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>aim is to enhance context relevance, answer faithfulness, and answer relevance</t>
+          <t>Finally, our metrics comparison reveals challenges in accurately measuring RAG system performance, suggesting that even our multifaceted evaluation approach may not capture all dimensions of answer quality relevant to financial domain experts.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>P06:abstract:0</t>
+          <t>P08:pdf:49; P08:pdf:14; P08:pdf:35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2882,24 +2467,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan benchmark RAG yang komprehensif karena benchmark saat ini memiliki skenario sempit dan dimensi evaluasi terbatas.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>current RAG benchmarks often suffer from narrow scenarios and limited evaluation dimensions</t>
+          <t>Accurate information retrieval is critical in financial Question-Answering (QA)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>P07:pdf:0</t>
+          <t>P09:pdf:2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2914,24 +2499,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Domain keuangan mencakup subdomain seperti perbankan investasi, asuransi, pasar modal, dan lainnya, dengan dokumen berbahasa Mandarin/Chinese yang diambil dari situs resmi dan berbagai format.</t>
+          <t>Dataset FINDER mencakup dokumen keuangan seperti artikel berita, filing, dan basis pengetahuan, berfokus pada bahasa Inggris dan tidak menyebutkan dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>finance is one of the most widespread vertical domains, comprising a wealth of professional knowledge</t>
+          <t>retrieving relevant documents (e.g., news articles, filings, and knowledge bases)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>P07:pdf:17; P07:pdf:14</t>
+          <t>P09:pdf:12; P09:pdf:10; P09:pdf:3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2946,24 +2531,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Menggunakan retriever seperti BGE-M3, BGE-large-zh, GTE-Qwen2-1.5b, dan jina-zh; generator LLM termasuk Qwen2.5-72B, Deepseek-v2-chat, Yi15-34B, Llama3.1-70B; chunking panjang 2048 dengan overlap 256.</t>
+          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>We set the retrieved document number as 5 to ensure a fair comparison</t>
+          <t>We use BM25 with standard parameters k1 = 1.2 and b = 0.75</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>P07:pdf:35; P07:pdf:10; P07:pdf:2</t>
+          <t>P09:pdf:30; P09:pdf:31; P09:pdf:28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2973,29 +2558,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik multi-aspek seperti ACC, HAL (hallucination), NAC (numerical accuracy), Rouge-L, serta MRR dan MAP untuk retriever.</t>
+          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hallucination (HAL). It assesses hallucinations in generated responses</t>
+          <t>Context Recall metric from RAGAS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>P07:pdf:29; P07:pdf:33; P07:pdf:26</t>
+          <t>P09:pdf:40; P09:pdf:2; P09:pdf:42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3010,24 +2595,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GTE-Qwen2-1.5B menunjukkan performa retrieval terbaik pada sebagian besar metrik; performa RAG bervariasi antar topik dan tugas, dan masih terdapat ruang besar untuk perbaikan.</t>
+          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>there remains a large space to improve RAG systems in vertical domains</t>
+          <t>E5-mistral demonstrates the best performance in all categories in terms of Context Recall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>P07:pdf:36; P07:pdf:10; P07:pdf:2</t>
+          <t>P09:pdf:35; P09:pdf:39; P09:pdf:42</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3037,29 +2622,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Keterbatasan meliputi kegagalan retriever pada topik ekor panjang, kegagalan generator dalam perhitungan keuangan, serta distribusi data yang masih terbatas dan berpotensi bias.</t>
+          <t>Penulis mencatat bahwa dataset sebelumnya tidak mencerminkan ambiguitas kueri dan proses retrieval yang penting untuk QA keuangan.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>the distribution remains somewhat limited</t>
+          <t>prior datasets ... failed to reflect the importance of ambiguous queries and the retrieval process</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>P07:pdf:47; P07:pdf:38; P07:pdf:14</t>
+          <t>P09:pdf:6; P09:pdf:29; P09:pdf:2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3074,24 +2659,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Inferensi: Paper tidak mengevaluasi kemampuan abstention atau faithfulness pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak mencakup fokus riset yang diinginkan.</t>
+          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>current RAG benchmarks often suffer from narrow scenarios and limited evaluation dimensions</t>
+          <t>Even state-of-the-art Large Language Models (LLMs) struggle with factual correctness in financial queries without proper context</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>P07:pdf:0</t>
+          <t>P09:pdf:4; P09:pdf:6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3101,29 +2686,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
+          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>These insights emphasize the importance of benchmarks that capture real-world document heterogeneity while enabling multifaceted evaluations aligned with the strengths and trade-offs of both models and methodologies.</t>
+          <t>Bayesian RAG: uncertainty-aware retrieval for reliable financial question answering</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>P08:pdf:12; P08:pdf:8; P08:pdf:11</t>
+          <t>P11:pdf:0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3138,24 +2723,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
+          <t>Fokus pada analisis dokumen keuangan regulasi berbahasa Inggris, menggunakan dataset seperti FinanceBench dengan dokumen laporan tahunan perusahaan.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FinDoc-RAG comprises 600+ QA pairs extracted from 46 documents in English from UBS AG and other UBS entities.</t>
+          <t>Financial document analysis demands precise factual extraction from complex regulatory filings</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>P08:pdf:5; P08:pdf:7; P08:pdf:4</t>
+          <t>P11:pdf:16; P11:pdf:2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3165,29 +2750,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
+          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vector-based (Vector-RAG) ... using cosine as the similarity metric.</t>
+          <t>Traditional RAG systems use deterministic embeddings that cannot quantify retrieval confidence</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>P08:pdf:50; P08:pdf:27; P08:pdf:25</t>
+          <t>P11:pdf:30; P11:pdf:23; P11:pdf:80</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3202,24 +2787,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
+          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>We computed accuracy as the mean proportion of CORRECT responses per question ... adopt the LLMLogScore (L3Score) metric.</t>
+          <t>Bayesian RAG reduces hallucination by 27.8% (from 0.18 to 0.13) and improves faithfulness by 6.1% (from 0.82 to 0.87)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>P08:pdf:22; P08:pdf:36; P08:pdf:35</t>
+          <t>P11:pdf:76; P11:pdf:75; P11:pdf:77</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3229,29 +2814,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
+          <t>Bayesian RAG meningkatkan faithfulness menjadi 0.87, menurunkan hallucination menjadi 0.13, dan memberikan kenaikan akurasi 25% dengan overhead latency 33 ms.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>leading systems achieve 0.91 accuracy in factual extraction but only 0.44 on multi-document synthesis tasks.</t>
+          <t>achieving 25% performance gains with 33 ms latency overhead</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>P08:pdf:12; P08:pdf:26; P08:pdf:40</t>
+          <t>P11:pdf:52; P11:pdf:102; P11:pdf:50</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3261,29 +2846,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Penulis mencatat keterbatasan LLM dalam penalaran kuantitatif, cakupan dokumen yang hanya sebagian dari keseluruhan domain, serta metrik yang belum sepenuhnya menangkap semua dimensi kualitas jawaban.</t>
+          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Current LLMs show limitations in quantitative reasoning and cross-document synthesis essential for financial applications.</t>
+          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>P08:pdf:2; P08:pdf:49; P08:pdf:6</t>
+          <t>P11:pdf:116; P11:pdf:2; P11:pdf:50</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3293,29 +2878,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finally, our metrics comparison reveals challenges in accurately measuring RAG system performance, suggesting that even our multifaceted evaluation approach may not capture all dimensions of answer quality relevant to financial domain experts.</t>
+          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>P08:pdf:49; P08:pdf:14; P08:pdf:35</t>
+          <t>P11:pdf:113; P11:pdf:2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3330,24 +2915,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
+          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Accurate information retrieval is critical in financial Question-Answering (QA)</t>
+          <t>To the best of our knowledge the present work is the first work that proposes a RAG approach that is hybrid of both VectorRAG and GraphRAG and demonstrates its potential of more effective analysis and utilization of financial documents</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>P09:pdf:2</t>
+          <t>P12:pdf:12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3362,24 +2947,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dataset FINDER mencakup dokumen keuangan seperti artikel berita, filing, dan basis pengetahuan, berfokus pada bahasa Inggris dan tidak menyebutkan dokumen perbankan Indonesia.</t>
+          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>retrieving relevant documents (e.g., news articles, filings, and knowledge bases)</t>
+          <t>Our methodology builds upon the concept of RAG ... leveraging both the power of large language models and the efficiency of semantic search.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>P09:pdf:12; P09:pdf:10; P09:pdf:3</t>
+          <t>P12:pdf:45; P12:pdf:41; P12:pdf:33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3389,29 +2974,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
+          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>We use BM25 with standard parameters k1 = 1.2 and b = 0.75</t>
+          <t>We employ OpenAI’s text-embedding-ada-002 model to transform textual data ... Chunk Size 1024</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>P09:pdf:30; P09:pdf:31; P09:pdf:28</t>
+          <t>P12:pdf:46; P12:pdf:6; P12:pdf:15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3421,29 +3006,29 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
+          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Context Recall metric from RAGAS</t>
+          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>P09:pdf:40; P09:pdf:2; P09:pdf:42</t>
+          <t>P12:pdf:27; P12:pdf:26; P12:pdf:33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3458,24 +3043,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
+          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>E5-mistral demonstrates the best performance in all categories in terms of Context Recall</t>
+          <t>HybridRAG ... excels in faithfulness, answer relevancy, and context recall</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>P09:pdf:35; P09:pdf:39; P09:pdf:42</t>
+          <t>P12:pdf:56; P12:pdf:60; P12:pdf:62</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3490,24 +3075,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Penulis mencatat bahwa dataset sebelumnya tidak mencerminkan ambiguitas kueri dan proses retrieval yang penting untuk QA keuangan.</t>
+          <t>GraphRAG kurang baik pada tugas Q&amp;A abstraktif dan ketika entitas tidak eksplisit; tantangan pada konteks panjang dan kualitas konteks yang tidak konsisten.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>prior datasets ... failed to reflect the importance of ambiguous queries and the retrieval process</t>
+          <t>GraphRAG generally underperforms in abstractive Q&amp;A tasks or when there is not explicit entity mentioned in the question</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>P09:pdf:6; P09:pdf:29; P09:pdf:2</t>
+          <t>P12:pdf:11; P12:pdf:12; P12:pdf:60</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3522,24 +3107,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
+          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Even state-of-the-art Large Language Models (LLMs) struggle with factual correctness in financial queries without proper context</t>
+          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>P09:pdf:4; P09:pdf:6</t>
+          <t>P12:pdf:27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3554,24 +3139,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Membangun benchmark FinRAGBench-V dan baseline RGenCite untuk RAG multimodal dengan visual citation.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Our task contains two main phases: the construction of FinRAGBench-V, and the implementation of the RGenCite baseline</t>
+          <t>demand for a Question Answering (QA) system capable of efficiently retrieving and analyzing compliance-related information</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>P10:pdf:17; P10:pdf:13</t>
+          <t>P13:pdf:5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3586,24 +3171,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Domain keuangan, mencakup laporan riset, laporan keuangan, prospektus, makalah akademik, dan majalah finansial; data dikumpulkan dari Qianzhan.com, FinGLM, BSCF, jurnal, dan Financial Times; ukuran besar dan berbahasa Inggris serta Mandarin.</t>
+          <t>Sistem diuji pada FinanceBench, dataset QA keuangan berbahasa Inggris dengan 150 pertanyaan tentang perusahaan publik, serta dokumen filing SEC.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Financial statements of companies and banks collected from the FinGLM dataset and official company and bank websites</t>
+          <t>FinanceBench ... includes 150 open-source questions relating to traded companies</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>P10:pdf:22; P10:pdf:13; P10:pdf:15</t>
+          <t>P13:pdf:42; P13:abstract:0; P13:pdf:0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3618,24 +3203,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Menggunakan retriever teksual (Jina-ColBERT-V2, Multilingual-E5-large) dan multimodal (ColQwen2, GME-Qwen2-VL-2B, DSE-QWen2-2b-MRL-V1); chunking pada level halaman; generator memakai MLLM seperti GPT-4o, GPT-4V, Gemini-2.0-Flash, Qwen2.5-VL-72B-Instruct; visual citation diintegrasikan pada tahap generasi.</t>
+          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>we develop the baseline system RGenCite, which covers both retrieval and generation, with visual citation seamlessly integrated into the generation stage</t>
+          <t>BM25 Sparse Retriever: ... BGE-M3 Dense Retriever: ... Metadata Retriever: ... HyDE Retriever</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>P10:pdf:10; P10:pdf:46; P10:pdf:30</t>
+          <t>P13:pdf:32; P13:pdf:29; P13:pdf:35</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3650,24 +3235,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup retrieval (nDCG@k, Recall@k, MRR@k), akurasi jawaban (ROUGE, ACC), serta kualitas visual citation (precision, recall pada level halaman dan blok, IoU, dan penilaian manusia 0-5).</t>
+          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>we adopt several evaluation metrics, namely nDCG@k (for k = 5, 10), Recall@k (for k = 5, 10), and MRR@k (k = 10)</t>
+          <t>adjusted Normalized Recall metric</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>P10:pdf:34; P10:pdf:50; P10:pdf:49</t>
+          <t>P13:pdf:53; P13:pdf:54; P13:pdf:50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3682,24 +3267,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Multimodal retriever mencapai recall@10 hingga 90.13 % (Chinese) dan 85.86 % (English), jauh di atas retriever teksual (42.71 %/36.36 %). Visual citation dengan image-cropping memperoleh korelasi Pearson 65.06 dengan IoU dan 68.01 dengan penilaian manusia.</t>
+          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ColQwen2 achieves a recall@10 of 90.13 (Chinese) and 85.86 (English)</t>
+          <t>FinSage achieves a significant improvement ... LLM accuracy of 49.66%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>P10:pdf:45; P10:pdf:51; P10:pdf:32</t>
+          <t>P13:pdf:61; P13:pdf:59; P13:pdf:62</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3714,24 +3299,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tidak melatih model khusus multimodal RAG untuk domain keuangan; benchmark berbahasa Inggris dan Mandarin, tidak mencakup bahasa Indonesia; belum mengatasi kebutuhan abstention.</t>
+          <t>Penulis mencatat kesulitan integrasi RAG ke dalam tugas kepatuhan keuangan karena keterbatasan domain dan tantangan multi-modalitas.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>we did not train a dedicated model for multimodal RAG in the financial domain</t>
+          <t>integration into financial compliance tasks can be difficult due to inherent domain-related limitations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>P10:pdf:52; P10:pdf:15; P10:pdf:4</t>
+          <t>P13:pdf:5; P13:pdf:15; P13:pdf:9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3746,24 +3331,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Penulis menyatakan belum melatih model khusus untuk RAG multimodal keuangan dan benchmark berbahasa Inggris/Mandarin, sehingga tidak mencakup dokumen perbankan berbahasa Indonesia atau evaluasi abstention. Inferensi: Karena tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia, gap penelitian tetap ada.</t>
+          <t>Inferensi: Meskipun FinSage meningkatkan akurasi dan recall pada dokumen filing berbahasa Inggris, tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga masih ada celah untuk menilai keandalan sistem RAG dalam konteks bahasa dan domain tersebut.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>we did not train a dedicated model for multimodal RAG in the financial domain</t>
+          <t>financial filings combine unstructured text ... conventional text-centric retrieval architectures fail to process cohesively</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>P10:pdf:52; P10:pdf:15</t>
+          <t>P13:pdf:5; P13:pdf:6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3773,29 +3358,29 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
+          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bayesian RAG: uncertainty-aware retrieval for reliable financial question answering</t>
+          <t>model must explicitly refrain from answering rather than fabricate an answer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>P11:pdf:0</t>
+          <t>P15:pdf:4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3805,29 +3390,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fokus pada analisis dokumen keuangan regulasi berbahasa Inggris, menggunakan dataset seperti FinanceBench dengan dokumen laporan tahunan perusahaan.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Financial document analysis demands precise factual extraction from complex regulatory filings</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>P11:pdf:16; P11:pdf:2</t>
-        </is>
-      </c>
+          <t>tidak disebut</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3837,29 +3414,29 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
+          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Traditional RAG systems use deterministic embeddings that cannot quantify retrieval confidence</t>
+          <t>we select Gemma 3 12B-IT ... 128K context window</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>P11:pdf:30; P11:pdf:23; P11:pdf:80</t>
+          <t>P15:pdf:11; P15:pdf:12; P15:pdf:1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3874,24 +3451,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
+          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bayesian RAG reduces hallucination by 27.8% (from 0.18 to 0.13) and improves faithfulness by 6.1% (from 0.82 to 0.87)</t>
+          <t>We evaluate along three dimensions: answer quality, refusal calibration, and latency</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>P11:pdf:76; P11:pdf:75; P11:pdf:77</t>
+          <t>P15:pdf:31; P15:pdf:5; P15:pdf:45</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3906,24 +3483,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bayesian RAG meningkatkan faithfulness menjadi 0.87, menurunkan hallucination menjadi 0.13, dan memberikan kenaikan akurasi 25% dengan overhead latency 33 ms.</t>
+          <t>FinRAG-12B meningkatkan resolution rate sebesar 7.1 poin persentase, mencapai F1 0.284 pada FinanceBench dengan tingkat kutipan 97.3%, serta menurunkan tingkat penolakan yang tidak tepat.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>achieving 25% performance gains with 33 ms latency overhead</t>
+          <t>FinRAG-12B improves the resolution rate by 7.1 percentage points</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>P11:pdf:52; P11:pdf:102; P11:pdf:50</t>
+          <t>P15:pdf:38; P15:pdf:40; P15:pdf:34</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3933,29 +3510,29 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
+          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
+          <t>An insufficient proportion of negative samples causes the model to default to its sycophantic prior</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>P11:pdf:116; P11:pdf:2; P11:pdf:50</t>
+          <t>P15:pdf:26; P15:pdf:35; P15:pdf:38</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3965,29 +3542,29 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
+          <t>our refusal evaluation captures explicit “I don’t know” responses and close variants, but may not fully account for hedged or partial uncertainty expressions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>P11:pdf:113; P11:pdf:2</t>
+          <t>P15:pdf:43; P15:pdf:46; P15:pdf:30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4002,24 +3579,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
+          <t>Masalahnya adalah mengevaluasi output LLM pada dokumen keuangan multimodal dengan metrik yang tepat.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>To the best of our knowledge the present work is the first work that proposes a RAG approach that is hybrid of both VectorRAG and GraphRAG and demonstrates its potential of more effective analysis and utilization of financial documents</t>
+          <t>Evaluating the output of LLM frameworks remains a significant open research area.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>P12:pdf:12</t>
+          <t>P16:pdf:32</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4034,24 +3611,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
+          <t>Dataset terdiri dari 300 pertanyaan QA yang dibuat dari dokumen keuangan SEC seperti Form 10-K, 10-Q, 8-K, dan DEF 14A, semuanya berbahasa Inggris.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Our methodology builds upon the concept of RAG ... leveraging both the power of large language models and the efficiency of semantic search.</t>
+          <t>For our evaluation, we collected financial documents from various companies, including Form 10-Q (Quarterly Report), Form 10-K (Annual Report), Form 8-K with EX-99.1 (Current Report), and DEF 14A (Proxy Statement).</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>P12:pdf:45; P12:pdf:41; P12:pdf:33</t>
+          <t>P16:pdf:25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4061,29 +3638,29 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
+          <t>MultiFinRAG menggunakan ekstraksi multimodal, embedding dengan threshold kesamaan modalitas, dan strategi fallback bertingkat dari teks ke tabel/gambar, serta DPR sebagai retriever.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>We employ OpenAI’s text-embedding-ada-002 model to transform textual data ... Chunk Size 1024</t>
+          <t>These outputs, along with narrative text, are embedded and indexed with modality-aware similarity thresholds for precise retrieval.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>P12:pdf:46; P12:pdf:6; P12:pdf:15</t>
+          <t>P16:pdf:1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4093,29 +3670,29 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
+          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
+          <t>we opt for manual evaluations. This approach ensures more accurate assessments and minimizes the risk of misjudgments.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>P12:pdf:27; P12:pdf:26; P12:pdf:33</t>
+          <t>P16:pdf:34</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4130,24 +3707,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
+          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HybridRAG ... excels in faithfulness, answer relevancy, and context recall</t>
+          <t>accuracy for text-based questions using MultiFinRAG with Gemma 3 is 90.4%, representing an improvement of 15.1% compared to the Baseline framework</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>P12:pdf:56; P12:pdf:60; P12:pdf:62</t>
+          <t>P16:pdf:34</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4157,29 +3734,29 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GraphRAG kurang baik pada tugas Q&amp;A abstraktif dan ketika entitas tidak eksplisit; tantangan pada konteks panjang dan kualitas konteks yang tidak konsisten.</t>
+          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GraphRAG generally underperforms in abstractive Q&amp;A tasks or when there is not explicit entity mentioned in the question</t>
+          <t>Detailed information-retrieval statistics (precision, recall, etc.) for the retrieval components were collected during development but are omitted here due to space constraints</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>P12:pdf:11; P12:pdf:12; P12:pdf:60</t>
+          <t>P16:pdf:32</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4194,24 +3771,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
+          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
+          <t>Questions require both text and image/table are the most challenging, as they require information from both text and images or tables.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>P12:pdf:27</t>
+          <t>P16:pdf:31</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4226,24 +3803,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
+          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>demand for a Question Answering (QA) system capable of efficiently retrieving and analyzing compliance-related information</t>
+          <t>robustness-precision trade-off</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>P13:pdf:5</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4258,24 +3835,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sistem diuji pada FinanceBench, dataset QA keuangan berbahasa Inggris dengan 150 pertanyaan tentang perusahaan publik, serta dokumen filing SEC.</t>
+          <t>Domain keuangan, menggunakan benchmark FinDER dengan 1.500 kueri pada lima grup; tipe dokumen regulasi, ukuran tidak disebut, bahasa tidak disebut.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FinanceBench ... includes 150 open-source questions relating to traded companies</t>
+          <t>FinDER benchmark (1,500 queries across five groups)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>P13:pdf:42; P13:abstract:0; P13:pdf:0</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4290,24 +3867,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
+          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BM25 Sparse Retriever: ... BGE-M3 Dense Retriever: ... Metadata Retriever: ... HyDE Retriever</t>
+          <t>Hybrid Document-Routed Retrieval (HDRR), a two-stage architecture that uses SFR as a document filter followed by chunk retrieval</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>P13:pdf:32; P13:pdf:29; P13:pdf:35</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4322,24 +3899,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
+          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>adjusted Normalized Recall metric</t>
+          <t>average score of 7.54 (25.2% above CBR, 16.9% above SFR)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>P13:pdf:53; P13:pdf:54; P13:pdf:50</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4354,24 +3931,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
+          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FinSage achieves a significant improvement ... LLM accuracy of 49.66%</t>
+          <t>6.4% failure rate, 67.7% correctness (+18.7 pp over CBR)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>P13:pdf:61; P13:pdf:59; P13:pdf:62</t>
+          <t>P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4381,29 +3958,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Penulis mencatat kesulitan integrasi RAG ke dalam tugas kepatuhan keuangan karena keterbatasan domain dan tantangan multi-modalitas.</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>integration into financial compliance tasks can be difficult due to inherent domain-related limitations</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>P13:pdf:5; P13:pdf:15; P13:pdf:9</t>
-        </is>
-      </c>
+          <t>tidak disebut</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4418,1985 +3987,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinSage meningkatkan akurasi dan recall pada dokumen filing berbahasa Inggris, tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga masih ada celah untuk menilai keandalan sistem RAG dalam konteks bahasa dan domain tersebut.</t>
+          <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>financial filings combine unstructured text ... conventional text-centric retrieval architectures fail to process cohesively</t>
+          <t>Hybrid Document-Routed Retrieval (HDRR) ... achieves the best performance on every metric</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>P13:pdf:5; P13:pdf:6</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Paper ini mengatasi masalah mendeteksi hallucination intrinsik pada sistem RAG multi-turn di domain keuangan Korea dengan fokus pada kesetiaan sumber.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>we focus exclusively on detecting intrinsic hallucinations based on source faithfulness</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>P14:abstract:1; P14:pdf:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Domainnya adalah keuangan Korea; menggunakan dataset “Korean Financial and Legal Document Machine Reading Comprehension” yang berisi dokumen keuangan dan hukum berbahasa Korea.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>We use the publicly available “Korean Financial and Legal Document Machine Reading Comprehension” dataset</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>P14:pdf:10; P14:pdf:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Pipeline otomatis menghasilkan split pelatihan; model generator 8B di-fine-tune dengan supervisi rasional, menggunakan embedding KURE Korean untuk chunking, dan retriever berbasis dokumen sumber.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>our construction pipeline can automatically generate a training split, on which a fine-tuned 8B model with rationale supervision</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>P14:pdf:8; P14:pdf:7; P14:pdf:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan klasifikasi biner (akurasi, presisi, recall, F1) serta klasifikasi empat kelas yang mencakup kemampuan menolak (refusal) dalam dialog multi-turn.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Binary classification determines the presence of a hallucination, reporting accuracy, precision, recall, and F1</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>P14:pdf:31; P14:pdf:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Model tertutup Gemini-2.5-Flash mencapai F1 tertinggi 0.860; abstention tetap menjadi aspek terlemah pada semua model yang diuji.</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Gemini-2.5-Flash achieving the highest F1 of 0.860</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>P14:pdf:35; P14:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Abstention yang tepat masih paling lemah; temuan terbatas pada bahasa Korea sehingga transferabilitas ke bahasa atau yurisdiksi lain terbatas.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>justified abstention remains the weakest axis across all evaluated models</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>P14:abstract:1; P14:pdf:32; P14:pdf:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun menyediakan benchmark RAG multi-turn untuk bahasa Korea, penelitian ini tidak mencakup bahasa Indonesia atau dokumen produk perbankan, sehingga belum mengevaluasi faithfulness dan abstention pada konteks Indonesia. Penulis juga mencatat bahwa temuan mereka terbatas pada bahasa Korea, sehingga transferabilitas ke bahasa lain tidak dijamin.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>the unique nature of the Korean</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>P14:pdf:4; P14:pdf:9; P14:pdf:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>model must explicitly refrain from answering rather than fabricate an answer</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>P15:pdf:4</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>we select Gemma 3 12B-IT ... 128K context window</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>P15:pdf:11; P15:pdf:12; P15:pdf:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>We evaluate along three dimensions: answer quality, refusal calibration, and latency</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>P15:pdf:31; P15:pdf:5; P15:pdf:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>FinRAG-12B meningkatkan resolution rate sebesar 7.1 poin persentase, mencapai F1 0.284 pada FinanceBench dengan tingkat kutipan 97.3%, serta menurunkan tingkat penolakan yang tidak tepat.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>FinRAG-12B improves the resolution rate by 7.1 percentage points</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>P15:pdf:38; P15:pdf:40; P15:pdf:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>An insufficient proportion of negative samples causes the model to default to its sycophantic prior</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>P15:pdf:26; P15:pdf:35; P15:pdf:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>our refusal evaluation captures explicit “I don’t know” responses and close variants, but may not fully account for hedged or partial uncertainty expressions</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>P15:pdf:43; P15:pdf:46; P15:pdf:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Masalahnya adalah mengevaluasi output LLM pada dokumen keuangan multimodal dengan metrik yang tepat.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Evaluating the output of LLM frameworks remains a significant open research area.</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>P16:pdf:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Dataset terdiri dari 300 pertanyaan QA yang dibuat dari dokumen keuangan SEC seperti Form 10-K, 10-Q, 8-K, dan DEF 14A, semuanya berbahasa Inggris.</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>For our evaluation, we collected financial documents from various companies, including Form 10-Q (Quarterly Report), Form 10-K (Annual Report), Form 8-K with EX-99.1 (Current Report), and DEF 14A (Proxy Statement).</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>P16:pdf:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>MultiFinRAG menggunakan ekstraksi multimodal, embedding dengan threshold kesamaan modalitas, dan strategi fallback bertingkat dari teks ke tabel/gambar, serta DPR sebagai retriever.</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>These outputs, along with narrative text, are embedded and indexed with modality-aware similarity thresholds for precise retrieval.</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>P16:pdf:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>we opt for manual evaluations. This approach ensures more accurate assessments and minimizes the risk of misjudgments.</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>P16:pdf:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>accuracy for text-based questions using MultiFinRAG with Gemma 3 is 90.4%, representing an improvement of 15.1% compared to the Baseline framework</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>P16:pdf:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>quote_not_found</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Detailed information-retrieval statistics (precision, recall, etc.) for the retrieval components were collected during development but are omitted here due to space constraints</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>P16:pdf:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Questions require both text and image/table are the most challenging, as they require information from both text and images or tables.</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>P16:pdf:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>robustness-precision trade-off</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
           <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Domain keuangan, menggunakan benchmark FinDER dengan 1.500 kueri pada lima grup; tipe dokumen regulasi, ukuran tidak disebut, bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>FinDER benchmark (1,500 queries across five groups)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Hybrid Document-Routed Retrieval (HDRR), a two-stage architecture that uses SFR as a document filter followed by chunk retrieval</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>average score of 7.54 (25.2% above CBR, 16.9% above SFR)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>6.4% failure rate, 67.7% correctness (+18.7 pp over CBR)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Hybrid Document-Routed Retrieval (HDRR) ... achieves the best performance on every metric</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Makalah mengidentifikasi tiga tantangan utama LLM multi-agent dalam keputusan berisiko tinggi: kontrol halusinasi, penggabungan penalaran semantik dengan simulasi numerik deterministik, serta auditabilitas end-to-end.</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Large language model (LLM)-based multi-agent systems face three open challenges in high-stakes decision support</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>P18:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Kerangka diuji pada domain stress testing keuangan menggunakan dataset publik (FRED, Yahoo Finance), perpustakaan 150 peristiwa krisis, dan 10 portofolio institusional sintetis.</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>public financial datasets (FRED, Yahoo Finance), a library of 150 curated crisis events, and 10 synthetic institutional portfolios</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>P18:abstract:0; P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent memperkenalkan pipeline retrieval-augmented generation dengan deterministic validation gates yang mengubah intent stres bahasa alami menjadi objek parameter ber-skema.</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>a retrieval-augmented generation (RAG) pipeline with deterministic validation gates</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>P18:abstract:0; P18:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup tingkat validitas 92.6% vs 78.4% (p&lt;0.001), peningkatan estimasi kerugian sistemik 52%, dan tingkat keberhasilan keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>92.6% validity rate versus 78.4% for RAG-augmented baselines (p&lt;0.001)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent mencapai validitas 92.6% (lebih tinggi 14.2 poin persentase), menghasilkan estimasi kerugian sistemik 52% lebih tinggi, dan sukses keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>92.6% validity rate versus 78.4% for RAG-augmented baselines</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>P18:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Validasi pada data institusional nyata belum dilakukan; penelitian masih bersifat proof-of-concept pada data sintetis dan publik.</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>validation on real institutional data is left to future work</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>P18:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Penulis tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia; mereka hanya menguji pada dataset publik berbahasa Inggris dan data sintetis. Inferensi: Oleh karena itu, belum ada analisis tentang bagaimana RAG menangani konteks bahasa Indonesia atau menolak menjawab bila konteks tidak memadai.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>validation on real institutional data is left to future work</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>P18:abstract:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi sistem RAG yang menjelaskan kontrak asuransi Quebec dengan fokus pada pengalaman pengguna secara manusiawi.</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>conducting a large-scale extrinsic study within the Quebec (francophone) insurance context</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>P19:pdf:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>quote_not_found</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Domainnya adalah asuransi kendaraan di Quebec, menggunakan dataset percakapan 3.759 pasangan pesan-jawaban dari 154 peserta yang mayoritas berbahasa Prancis.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Study Sample Our user study successfully concluded with the collection of complete responses from 154 participants, along with the 3,759 message-answer pairs</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>P19:pdf:11; P19:pdf:12; P19:pdf:5</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Sistem menggunakan model LLM OpenAI “o3-2025-04-16” dengan arsitektur RAG standar, namun detail retriever dan strategi chunking tidak dijelaskan.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>The insurance RAG system under evaluation utilizes OpenAI “o3-2025-04-16” LLM, along with the same RAG as described in [5]</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>P19:pdf:11; P19:pdf:5; P19:pdf:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup survei Likert 7-point, analisis statistik t-test, Kruskal-Wallis, dan korelasi Pearson untuk mengukur kepuasan, usaha kognitif, dan kepercayaan.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Most questions utilized a 7-point Likert scale</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>P19:pdf:13; P19:pdf:15; P19:pdf:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Pengguna dengan literasi rendah melaporkan kepuasan secara signifikan lebih tinggi, sementara manfaat inti sistem diakui secara universal oleh semua kelompok.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>reported significantly higher overall satisfaction than their high-literacy counterparts</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>P19:pdf:21; P19:pdf:22; P19:pdf:8</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Penulis mencatat adanya kesalahan faktual, preferensi pengguna terhadap agen manusia, serta keterbatasan generalisasi karena sampel berpendidikan tinggi dan setting eksperimental.</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>the system is not yet ready for fully autonomous, unsupervised public deployment</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>P19:pdf:37; P19:pdf:38; P19:pdf:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention RAG pada dokumen perbankan berbahasa Indonesia; fokusnya terbatas pada konteks asuransi Quebec berbahasa Prancis. Inferensi: Karena tidak ada pengujian terhadap keakuratan faktual atau penolakan ketika konteks tidak memadai, gap muncul untuk aplikasi bahasa Indonesia di domain perbankan.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>may not be fully generalizable to a broader, more diverse demographic</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>P19:pdf:41; P19:pdf:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi dua pendekatan peningkatan performa LLM, yaitu fine-tuning dan retrieval-augmented generation (RAG), untuk mendukung pengambilan keputusan hukum dalam konteks pajak pertambahan nilai (VAT).</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Methods This study experimentally evaluates two common approaches for enhancing LLM performance—fine-tuning and retrieval-augmented generation (RAG)</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>P20:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Domainnya adalah pajak nilai tambah (VAT) di Austria/EU, menggunakan kasus VAT dari buku teks serta kasus nyata dari firma konsultan pajak; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>applied to both textbook VAT cases and real-world cases from a tax consulting firm</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>LLM yang dikonfigurasi dengan tepat dapat secara efektif mendukung profesional pajak dalam tugas-tugas VAT, mengotomatisasi pekerjaan rutin, dan menghasilkan justifikasi hukum yang kuat.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Properly configured LLMs can effectively support tax professionals in VAT-related tasks, automating routine work, providing initial analyses, and generating legally grounded justifications for decisions</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Prototipe belum siap untuk otomatisasi penuh karena sensitivitas domain hukum, serta masih terdapat keterbatasan dalam menangani pengetahuan implisit klien dan dokumentasi kontekstual.</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>current prototypes are not yet ready for full automation given the sensitivity of the legal domain, and limitations persist in handling implicit client knowledge and context-specific documentation</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>P20:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Inferensi: Makalah ini tidak membahas faithfulness atau abstention pada sistem RAG, tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga tidak menjawab fokus penelitian yang menilai kemampuan RAG dalam konteks tersebut.</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>LLMs show strong potential to assist tax consultants by reducing workload and supporting VAT decision-making</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi peluncuran pilot GenAI "no-regret" dalam satu kuartal untuk meningkatkan nilai pada Alpes Bank.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>deliver a “no-regret” GenAI pilot within one quarter</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Studi kasus pada Alpes Bank, bank universal Swiss, menggunakan email inquiry sebagai data; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Alpes Bank, a Swiss universal bank whose branch-centric, premium-service model is challenged by generative AI</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Tim membangun email assistant berbasis retrieval-augmented generation (RAG) bekerja sama dengan AILabs; detail teknis tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>builds a retrieval-augmented generation (RAG) email assistant with an external partner (i.e., AILabs)</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan dengan mengukur pengurangan waktu penanganan inquiry rutin, tercatat penurunan 21%.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>the GenAI email assistant reduces handling time for routine inquiries by 21%</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Email assistant berbasis GenAI mengurangi waktu penanganan inquiry rutin sebesar 21%.</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>the GenAI email assistant reduces handling time for routine inquiries by 21%</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Inferensi: Penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak menjawab fokus riset yang diusulkan.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Bank move from a special-project setup to an organizational design and governance process that supports enterprise-wide scaling</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>P21:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Penelitian ini memperkenalkan NextRAG, kerangka Retrieval-Augmented Generation bilingual untuk meningkatkan penelusuran pengetahuan keuangan dan menjawab pertanyaan.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>This study introduces NextRAG, a bilingual Retrieval-Augmented Generation (RAG) framework for financial knowledge retrieval and question answering</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>P22:abstract:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Fokus pada dokumen keuangan multibahasa dari institusi dan regulator di Bangladesh, serta dataset Q&amp;A keuangan bilingual yang beragam.</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Financial institutions and regulators produce large volumes of complex, multilingual documents... Evaluation on a diverse bilingual financial Q&amp;A dataset</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Menggunakan retrieval sparse BM25 dengan smoothing Dirichlet, fusi Reciprocal Rank Fusion, re-ranking cross-encoder, serta prompting yang sadar bahasa untuk Bangla dan Inggris.</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>NextRAG employs specialized preprocessing... integrates sparse retrieval with BM25, probabilistic query modeling via Dirichlet smoothing, and fuses results using Reciprocal Rank Fusion (RRF), followed by cross-encoder re-ranking</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Dievaluasi pada dataset Q&amp;A bilingual dengan metrik mean cosine similarity dan F1 score, membandingkan dengan RAG konvensional.</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>achieving a mean cosine similarity of 0.77 and an F1 score of 68.3%</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>P22:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>NextRAG secara konsisten mengungguli RAG konvensional, memperoleh mean cosine similarity 0.77 dan F1 68.3%.</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>NextRAG consistently outperforms conventional RAG, achieving a mean cosine similarity of 0.77 and an F1 score of 68.3%</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>P22:abstract:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun NextRAG menangani dokumen bilingual, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diinginkan.</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Bangladeshi context... low-resource bilingual setting</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
         </is>
       </c>
     </row>
